--- a/project2/Project2.xlsx
+++ b/project2/Project2.xlsx
@@ -1828,6 +1828,14 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
+        <c:dLbls>
+          <c:showBubbleSize val="0"/>
+          <c:showCatName val="0"/>
+          <c:showLegendKey val="0"/>
+          <c:showPercent val="0"/>
+          <c:showSerName val="0"/>
+          <c:showVal val="0"/>
+        </c:dLbls>
         <c:marker val="0"/>
         <c:smooth val="0"/>
         <c:axId val="2140841519"/>
@@ -1996,7 +2004,7 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0" flipH="0" flipV="0">
-      <a:off x="7178039" y="723899"/>
+      <a:off x="6568438" y="723898"/>
       <a:ext cx="8493011" cy="5084444"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
@@ -2631,16 +2639,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:w="http://schemas.openxmlformats.org/wordprocessingml/2006/main">
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>594359</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>899158</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>175259</xdr:rowOff>
+      <xdr:rowOff>175258</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>552971</xdr:colOff>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>552969</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>139064</xdr:rowOff>
+      <xdr:rowOff>139062</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2650,7 +2658,7 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0" flipH="0" flipV="0">
-        <a:off x="7178039" y="723899"/>
+        <a:off x="6568438" y="723898"/>
         <a:ext cx="8493011" cy="5084444"/>
       </xdr:xfrm>
       <a:graphic>
@@ -3176,7 +3184,7 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
     </row>
@@ -3191,7 +3199,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <f>(I2-32)*5/9</f>
+        <f>(H2-32)*5/9</f>
         <v>-17.777777777777779</v>
       </c>
       <c r="E2">
@@ -3203,7 +3211,7 @@
       <c r="G2">
         <v>0</v>
       </c>
-      <c r="I2">
+      <c r="H2">
         <v>0</v>
       </c>
     </row>
@@ -3218,7 +3226,7 @@
         <v>15.375037000000001</v>
       </c>
       <c r="D3">
-        <f>(I3-32)*5/9</f>
+        <f>(H3-32)*5/9</f>
         <v>6.5252900000000009</v>
       </c>
       <c r="E3">
@@ -3230,7 +3238,7 @@
       <c r="G3">
         <v>1</v>
       </c>
-      <c r="I3">
+      <c r="H3">
         <v>43.745522000000001</v>
       </c>
     </row>
@@ -3245,7 +3253,7 @@
         <v>14.585760000000001</v>
       </c>
       <c r="D4">
-        <f>(I4-32)*5/9</f>
+        <f>(H4-32)*5/9</f>
         <v>17.25364888888889</v>
       </c>
       <c r="E4">
@@ -3257,7 +3265,7 @@
       <c r="G4">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="H4">
         <v>63.056567999999999</v>
       </c>
     </row>
@@ -3272,7 +3280,7 @@
         <v>14.906654</v>
       </c>
       <c r="D5">
-        <f>(I5-32)*5/9</f>
+        <f>(H5-32)*5/9</f>
         <v>21.411653888888889</v>
       </c>
       <c r="E5">
@@ -3284,7 +3292,7 @@
       <c r="G5">
         <v>1</v>
       </c>
-      <c r="I5">
+      <c r="H5">
         <v>70.540976999999998</v>
       </c>
     </row>
@@ -3299,7 +3307,7 @@
         <v>14.758124</v>
       </c>
       <c r="D6">
-        <f>(I6-32)*5/9</f>
+        <f>(H6-32)*5/9</f>
         <v>23.161154999999997</v>
       </c>
       <c r="E6">
@@ -3311,7 +3319,7 @@
       <c r="G6">
         <v>1</v>
       </c>
-      <c r="I6">
+      <c r="H6">
         <v>73.690078999999997</v>
       </c>
     </row>
@@ -3326,7 +3334,7 @@
         <v>13.361834</v>
       </c>
       <c r="D7">
-        <f>(I7-32)*5/9</f>
+        <f>(H7-32)*5/9</f>
         <v>26.436962777777779</v>
       </c>
       <c r="E7">
@@ -3338,7 +3346,7 @@
       <c r="G7">
         <v>0</v>
       </c>
-      <c r="I7">
+      <c r="H7">
         <v>79.586533000000003</v>
       </c>
     </row>
@@ -3353,7 +3361,7 @@
         <v>9.3162730000000007</v>
       </c>
       <c r="D8">
-        <f>(I8-32)*5/9</f>
+        <f>(H8-32)*5/9</f>
         <v>27.795969444444449</v>
       </c>
       <c r="E8">
@@ -3365,7 +3373,7 @@
       <c r="G8">
         <v>0</v>
       </c>
-      <c r="I8">
+      <c r="H8">
         <v>82.032745000000006</v>
       </c>
     </row>
@@ -3380,7 +3388,7 @@
         <v>3.822562</v>
       </c>
       <c r="D9">
-        <f>(I9-32)*5/9</f>
+        <f>(H9-32)*5/9</f>
         <v>24.600838333333332</v>
       </c>
       <c r="E9">
@@ -3392,7 +3400,7 @@
       <c r="G9">
         <v>0</v>
       </c>
-      <c r="I9">
+      <c r="H9">
         <v>76.281509</v>
       </c>
     </row>
@@ -3407,7 +3415,7 @@
         <v>5.4211520000000002</v>
       </c>
       <c r="D10">
-        <f>(I10-32)*5/9</f>
+        <f>(H10-32)*5/9</f>
         <v>14.400560555555554</v>
       </c>
       <c r="E10">
@@ -3419,7 +3427,7 @@
       <c r="G10">
         <v>0</v>
       </c>
-      <c r="I10">
+      <c r="H10">
         <v>57.921008999999998</v>
       </c>
     </row>
@@ -3434,7 +3442,7 @@
         <v>2.7236069999999999</v>
       </c>
       <c r="D11">
-        <f>(I11-32)*5/9</f>
+        <f>(H11-32)*5/9</f>
         <v>11.57917</v>
       </c>
       <c r="E11">
@@ -3446,7 +3454,7 @@
       <c r="G11">
         <v>0</v>
       </c>
-      <c r="I11">
+      <c r="H11">
         <v>52.842506</v>
       </c>
     </row>
@@ -3461,7 +3469,7 @@
         <v>4.6303859999999997</v>
       </c>
       <c r="D12">
-        <f>(I12-32)*5/9</f>
+        <f>(H12-32)*5/9</f>
         <v>13.242420555555555</v>
       </c>
       <c r="E12">
@@ -3473,7 +3481,7 @@
       <c r="G12">
         <v>0</v>
       </c>
-      <c r="I12">
+      <c r="H12">
         <v>55.836357</v>
       </c>
     </row>
@@ -3488,7 +3496,7 @@
         <v>8.8976469999999992</v>
       </c>
       <c r="D13">
-        <f>(I13-32)*5/9</f>
+        <f>(H13-32)*5/9</f>
         <v>8.5909566666666635</v>
       </c>
       <c r="E13">
@@ -3500,7 +3508,7 @@
       <c r="G13">
         <v>0</v>
       </c>
-      <c r="I13">
+      <c r="H13">
         <v>47.463721999999997</v>
       </c>
     </row>
@@ -3515,7 +3523,7 @@
         <v>11.650064</v>
       </c>
       <c r="D14">
-        <f>(I14-32)*5/9</f>
+        <f>(H14-32)*5/9</f>
         <v>6.3514050000000015</v>
       </c>
       <c r="E14">
@@ -3527,7 +3535,7 @@
       <c r="G14">
         <v>0</v>
       </c>
-      <c r="I14">
+      <c r="H14">
         <v>43.432529000000002</v>
       </c>
     </row>
@@ -3542,7 +3550,7 @@
         <v>13.412706999999999</v>
       </c>
       <c r="D15">
-        <f>(I15-32)*5/9</f>
+        <f>(H15-32)*5/9</f>
         <v>12.951870000000001</v>
       </c>
       <c r="E15">
@@ -3554,7 +3562,7 @@
       <c r="G15">
         <v>1</v>
       </c>
-      <c r="I15">
+      <c r="H15">
         <v>55.313366000000002</v>
       </c>
     </row>
@@ -3569,7 +3577,7 @@
         <v>16.875209999999999</v>
       </c>
       <c r="D16">
-        <f>(I16-32)*5/9</f>
+        <f>(H16-32)*5/9</f>
         <v>12.976956111111113</v>
       </c>
       <c r="E16">
@@ -3581,7 +3589,7 @@
       <c r="G16">
         <v>2</v>
       </c>
-      <c r="I16">
+      <c r="H16">
         <v>55.358521000000003</v>
       </c>
     </row>
@@ -3596,7 +3604,7 @@
         <v>14.928813999999999</v>
       </c>
       <c r="D17">
-        <f>(I17-32)*5/9</f>
+        <f>(H17-32)*5/9</f>
         <v>22.781651666666669</v>
       </c>
       <c r="E17">
@@ -3608,7 +3616,7 @@
       <c r="G17">
         <v>2</v>
       </c>
-      <c r="I17">
+      <c r="H17">
         <v>73.006973000000002</v>
       </c>
     </row>
@@ -3623,7 +3631,7 @@
         <v>15.918747</v>
       </c>
       <c r="D18">
-        <f>(I18-32)*5/9</f>
+        <f>(H18-32)*5/9</f>
         <v>26.831461666666669</v>
       </c>
       <c r="E18">
@@ -3635,7 +3643,7 @@
       <c r="G18">
         <v>4</v>
       </c>
-      <c r="I18">
+      <c r="H18">
         <v>80.296631000000005</v>
       </c>
     </row>
@@ -3650,7 +3658,7 @@
         <v>11.656897000000001</v>
       </c>
       <c r="D19">
-        <f>(I19-32)*5/9</f>
+        <f>(H19-32)*5/9</f>
         <v>31.280585555555554</v>
       </c>
       <c r="E19">
@@ -3662,7 +3670,7 @@
       <c r="G19">
         <v>6</v>
       </c>
-      <c r="I19">
+      <c r="H19">
         <v>88.305053999999998</v>
       </c>
     </row>
@@ -3677,7 +3685,7 @@
         <v>9.0999929999999996</v>
       </c>
       <c r="D20">
-        <f>(I20-32)*5/9</f>
+        <f>(H20-32)*5/9</f>
         <v>22.868215555555558</v>
       </c>
       <c r="E20">
@@ -3689,7 +3697,7 @@
       <c r="G20">
         <v>5</v>
       </c>
-      <c r="I20">
+      <c r="H20">
         <v>73.162788000000006</v>
       </c>
     </row>
@@ -3704,7 +3712,7 @@
         <v>4.0140450000000003</v>
       </c>
       <c r="D21">
-        <f>(I21-32)*5/9</f>
+        <f>(H21-32)*5/9</f>
         <v>21.733330555555558</v>
       </c>
       <c r="E21">
@@ -3716,7 +3724,7 @@
       <c r="G21">
         <v>7</v>
       </c>
-      <c r="I21">
+      <c r="H21">
         <v>71.119995000000003</v>
       </c>
     </row>
@@ -3731,7 +3739,7 @@
         <v>2.4568279999999998</v>
       </c>
       <c r="D22">
-        <f>(I22-32)*5/9</f>
+        <f>(H22-32)*5/9</f>
         <v>17.961341111111114</v>
       </c>
       <c r="E22">
@@ -3743,7 +3751,7 @@
       <c r="G22">
         <v>6</v>
       </c>
-      <c r="I22">
+      <c r="H22">
         <v>64.330414000000005</v>
       </c>
     </row>
@@ -3758,7 +3766,7 @@
         <v>5.8132770000000002</v>
       </c>
       <c r="D23">
-        <f>(I23-32)*5/9</f>
+        <f>(H23-32)*5/9</f>
         <v>17.909054444444447</v>
       </c>
       <c r="E23">
@@ -3770,7 +3778,7 @@
       <c r="G23">
         <v>5</v>
       </c>
-      <c r="I23">
+      <c r="H23">
         <v>64.236298000000005</v>
       </c>
     </row>
@@ -3785,7 +3793,7 @@
         <v>5.9164000000000003</v>
       </c>
       <c r="D24">
-        <f>(I24-32)*5/9</f>
+        <f>(H24-32)*5/9</f>
         <v>5.1062138888888873</v>
       </c>
       <c r="E24">
@@ -3797,7 +3805,7 @@
       <c r="G24">
         <v>4</v>
       </c>
-      <c r="I24">
+      <c r="H24">
         <v>41.191184999999997</v>
       </c>
     </row>
@@ -3812,7 +3820,7 @@
         <v>8.4972290000000008</v>
       </c>
       <c r="D25">
-        <f>(I25-32)*5/9</f>
+        <f>(H25-32)*5/9</f>
         <v>7.7146977777777801</v>
       </c>
       <c r="E25">
@@ -3824,7 +3832,7 @@
       <c r="G25">
         <v>3</v>
       </c>
-      <c r="I25">
+      <c r="H25">
         <v>45.886456000000003</v>
       </c>
     </row>
@@ -3839,7 +3847,7 @@
         <v>9.7100360000000006</v>
       </c>
       <c r="D26">
-        <f>(I26-32)*5/9</f>
+        <f>(H26-32)*5/9</f>
         <v>5.1742300000000006</v>
       </c>
       <c r="E26">
@@ -3851,7 +3859,7 @@
       <c r="G26">
         <v>2</v>
       </c>
-      <c r="I26">
+      <c r="H26">
         <v>41.313614000000001</v>
       </c>
     </row>
@@ -3866,7 +3874,7 @@
         <v>15.965878999999999</v>
       </c>
       <c r="D27">
-        <f>(I27-32)*5/9</f>
+        <f>(H27-32)*5/9</f>
         <v>12.496982222222222</v>
       </c>
       <c r="E27">
@@ -3878,7 +3886,7 @@
       <c r="G27">
         <v>1</v>
       </c>
-      <c r="I27">
+      <c r="H27">
         <v>54.494568000000001</v>
       </c>
     </row>
@@ -3893,7 +3901,7 @@
         <v>16.749693000000001</v>
       </c>
       <c r="D28">
-        <f>(I28-32)*5/9</f>
+        <f>(H28-32)*5/9</f>
         <v>10.283048333333333</v>
       </c>
       <c r="E28">
@@ -3905,7 +3913,7 @@
       <c r="G28">
         <v>0</v>
       </c>
-      <c r="I28">
+      <c r="H28">
         <v>50.509487</v>
       </c>
     </row>
@@ -3920,7 +3928,7 @@
         <v>16.547001000000002</v>
       </c>
       <c r="D29">
-        <f>(I29-32)*5/9</f>
+        <f>(H29-32)*5/9</f>
         <v>16.809643888888889</v>
       </c>
       <c r="E29">
@@ -3932,7 +3940,7 @@
       <c r="G29">
         <v>0</v>
       </c>
-      <c r="I29">
+      <c r="H29">
         <v>62.257359000000001</v>
       </c>
     </row>
@@ -3947,7 +3955,7 @@
         <v>15.762941</v>
       </c>
       <c r="D30">
-        <f>(I30-32)*5/9</f>
+        <f>(H30-32)*5/9</f>
         <v>22.746793888888892</v>
       </c>
       <c r="E30">
@@ -3959,7 +3967,7 @@
       <c r="G30">
         <v>1</v>
       </c>
-      <c r="I30">
+      <c r="H30">
         <v>72.944229000000007</v>
       </c>
     </row>
@@ -3974,7 +3982,7 @@
         <v>10.468787000000001</v>
       </c>
       <c r="D31">
-        <f>(I31-32)*5/9</f>
+        <f>(H31-32)*5/9</f>
         <v>24.402919444444446</v>
       </c>
       <c r="E31">
@@ -3986,7 +3994,7 @@
       <c r="G31">
         <v>1</v>
       </c>
-      <c r="I31">
+      <c r="H31">
         <v>75.925255000000007</v>
       </c>
     </row>
@@ -4001,7 +4009,7 @@
         <v>9.1937650000000009</v>
       </c>
       <c r="D32">
-        <f>(I32-32)*5/9</f>
+        <f>(H32-32)*5/9</f>
         <v>24.625396666666671</v>
       </c>
       <c r="E32">
@@ -4013,7 +4021,7 @@
       <c r="G32">
         <v>2</v>
       </c>
-      <c r="I32">
+      <c r="H32">
         <v>76.325714000000005</v>
       </c>
     </row>
@@ -4028,7 +4036,7 @@
         <v>6.3865759999999998</v>
       </c>
       <c r="D33">
-        <f>(I33-32)*5/9</f>
+        <f>(H33-32)*5/9</f>
         <v>24.397188888888891</v>
       </c>
       <c r="E33">
@@ -4040,7 +4048,7 @@
       <c r="G33">
         <v>2</v>
       </c>
-      <c r="I33">
+      <c r="H33">
         <v>75.914940000000001</v>
       </c>
     </row>
@@ -4055,7 +4063,7 @@
         <v>5.9003240000000003</v>
       </c>
       <c r="D34">
-        <f>(I34-32)*5/9</f>
+        <f>(H34-32)*5/9</f>
         <v>17.759763888888887</v>
       </c>
       <c r="E34">
@@ -4067,7 +4075,7 @@
       <c r="G34">
         <v>2</v>
       </c>
-      <c r="I34">
+      <c r="H34">
         <v>63.967574999999997</v>
       </c>
     </row>
@@ -4082,7 +4090,7 @@
         <v>4.941319</v>
       </c>
       <c r="D35">
-        <f>(I35-32)*5/9</f>
+        <f>(H35-32)*5/9</f>
         <v>16.177198888888888</v>
       </c>
       <c r="E35">
@@ -4094,7 +4102,7 @@
       <c r="G35">
         <v>2</v>
       </c>
-      <c r="I35">
+      <c r="H35">
         <v>61.118957999999999</v>
       </c>
     </row>
@@ -4109,7 +4117,7 @@
         <v>4.6206579999999997</v>
       </c>
       <c r="D36">
-        <f>(I36-32)*5/9</f>
+        <f>(H36-32)*5/9</f>
         <v>7.5042683333333331</v>
       </c>
       <c r="E36">
@@ -4121,7 +4129,7 @@
       <c r="G36">
         <v>1</v>
       </c>
-      <c r="I36">
+      <c r="H36">
         <v>45.507683</v>
       </c>
     </row>
@@ -4136,7 +4144,7 @@
         <v>7.0377270000000003</v>
       </c>
       <c r="D37">
-        <f>(I37-32)*5/9</f>
+        <f>(H37-32)*5/9</f>
         <v>9.4911361111111123</v>
       </c>
       <c r="E37">
@@ -4148,7 +4156,7 @@
       <c r="G37">
         <v>0</v>
       </c>
-      <c r="I37">
+      <c r="H37">
         <v>49.084045000000003</v>
       </c>
     </row>
@@ -4163,7 +4171,7 @@
         <v>11.280728</v>
       </c>
       <c r="D38">
-        <f>(I38-32)*5/9</f>
+        <f>(H38-32)*5/9</f>
         <v>6.3906100000000006</v>
       </c>
       <c r="E38">
@@ -4175,7 +4183,7 @@
       <c r="G38">
         <v>0</v>
       </c>
-      <c r="I38">
+      <c r="H38">
         <v>43.503098000000001</v>
       </c>
     </row>
@@ -4190,7 +4198,7 @@
         <v>15.386649</v>
       </c>
       <c r="D39">
-        <f>(I39-32)*5/9</f>
+        <f>(H39-32)*5/9</f>
         <v>5.2661405555555554</v>
       </c>
       <c r="E39">
@@ -4202,7 +4210,7 @@
       <c r="G39">
         <v>1</v>
       </c>
-      <c r="I39">
+      <c r="H39">
         <v>41.479053</v>
       </c>
     </row>
@@ -4217,7 +4225,7 @@
         <v>14.699982</v>
       </c>
       <c r="D40">
-        <f>(I40-32)*5/9</f>
+        <f>(H40-32)*5/9</f>
         <v>12.091272222222223</v>
       </c>
       <c r="E40">
@@ -4229,7 +4237,7 @@
       <c r="G40">
         <v>1</v>
       </c>
-      <c r="I40">
+      <c r="H40">
         <v>53.764290000000003</v>
       </c>
     </row>
@@ -4244,7 +4252,7 @@
         <v>16.021329999999999</v>
       </c>
       <c r="D41">
-        <f>(I41-32)*5/9</f>
+        <f>(H41-32)*5/9</f>
         <v>15.945042777777777</v>
       </c>
       <c r="E41">
@@ -4256,7 +4264,7 @@
       <c r="G41">
         <v>2</v>
       </c>
-      <c r="I41">
+      <c r="H41">
         <v>60.701076999999998</v>
       </c>
     </row>
@@ -4271,7 +4279,7 @@
         <v>15.869856</v>
       </c>
       <c r="D42">
-        <f>(I42-32)*5/9</f>
+        <f>(H42-32)*5/9</f>
         <v>19.741266111111109</v>
       </c>
       <c r="E42">
@@ -4283,7 +4291,7 @@
       <c r="G42">
         <v>2</v>
       </c>
-      <c r="I42">
+      <c r="H42">
         <v>67.534278999999998</v>
       </c>
     </row>
@@ -4298,7 +4306,7 @@
         <v>11.534691</v>
       </c>
       <c r="D43">
-        <f>(I43-32)*5/9</f>
+        <f>(H43-32)*5/9</f>
         <v>22.133343888888888</v>
       </c>
       <c r="E43">
@@ -4310,7 +4318,7 @@
       <c r="G43">
         <v>2</v>
       </c>
-      <c r="I43">
+      <c r="H43">
         <v>71.840018999999998</v>
       </c>
     </row>
@@ -4325,7 +4333,7 @@
         <v>10.187101</v>
       </c>
       <c r="D44">
-        <f>(I44-32)*5/9</f>
+        <f>(H44-32)*5/9</f>
         <v>31.674190000000003</v>
       </c>
       <c r="E44">
@@ -4337,7 +4345,7 @@
       <c r="G44">
         <v>1</v>
       </c>
-      <c r="I44">
+      <c r="H44">
         <v>89.013542000000001</v>
       </c>
     </row>
@@ -4352,7 +4360,7 @@
         <v>6.756443</v>
       </c>
       <c r="D45">
-        <f>(I45-32)*5/9</f>
+        <f>(H45-32)*5/9</f>
         <v>22.114389444444448</v>
       </c>
       <c r="E45">
@@ -4364,7 +4372,7 @@
       <c r="G45">
         <v>0</v>
       </c>
-      <c r="I45">
+      <c r="H45">
         <v>71.805901000000006</v>
       </c>
     </row>
@@ -4379,7 +4387,7 @@
         <v>3.1334909999999998</v>
       </c>
       <c r="D46">
-        <f>(I46-32)*5/9</f>
+        <f>(H46-32)*5/9</f>
         <v>16.144214444444444</v>
       </c>
       <c r="E46">
@@ -4391,7 +4399,7 @@
       <c r="G46">
         <v>0</v>
       </c>
-      <c r="I46">
+      <c r="H46">
         <v>61.059586000000003</v>
       </c>
     </row>
@@ -4406,7 +4414,7 @@
         <v>2.8140040000000002</v>
       </c>
       <c r="D47">
-        <f>(I47-32)*5/9</f>
+        <f>(H47-32)*5/9</f>
         <v>9.8399311111111079</v>
       </c>
       <c r="E47">
@@ -4418,7 +4426,7 @@
       <c r="G47">
         <v>0</v>
       </c>
-      <c r="I47">
+      <c r="H47">
         <v>49.711875999999997</v>
       </c>
     </row>
@@ -4433,7 +4441,7 @@
         <v>6.9312399999999998</v>
       </c>
       <c r="D48">
-        <f>(I48-32)*5/9</f>
+        <f>(H48-32)*5/9</f>
         <v>3.5374261111111118</v>
       </c>
       <c r="E48">
@@ -4445,7 +4453,7 @@
       <c r="G48">
         <v>0</v>
       </c>
-      <c r="I48">
+      <c r="H48">
         <v>38.367367000000002</v>
       </c>
     </row>
@@ -4460,7 +4468,7 @@
         <v>6.7452059999999996</v>
       </c>
       <c r="D49">
-        <f>(I49-32)*5/9</f>
+        <f>(H49-32)*5/9</f>
         <v>7.546060555555556</v>
       </c>
       <c r="E49">
@@ -4472,7 +4480,7 @@
       <c r="G49">
         <v>0</v>
       </c>
-      <c r="I49">
+      <c r="H49">
         <v>45.582909000000001</v>
       </c>
     </row>
@@ -4487,7 +4495,7 @@
         <v>11.639168</v>
       </c>
       <c r="D50">
-        <f>(I50-32)*5/9</f>
+        <f>(H50-32)*5/9</f>
         <v>-0.14885055555555601</v>
       </c>
       <c r="E50">
@@ -4499,7 +4507,7 @@
       <c r="G50">
         <v>1</v>
       </c>
-      <c r="I50">
+      <c r="H50">
         <v>31.732068999999999</v>
       </c>
     </row>
@@ -4514,7 +4522,7 @@
         <v>15.433832000000001</v>
       </c>
       <c r="D51">
-        <f>(I51-32)*5/9</f>
+        <f>(H51-32)*5/9</f>
         <v>4.8106172222222234</v>
       </c>
       <c r="E51">
@@ -4526,7 +4534,7 @@
       <c r="G51">
         <v>2</v>
       </c>
-      <c r="I51">
+      <c r="H51">
         <v>40.659111000000003</v>
       </c>
     </row>
@@ -4541,7 +4549,7 @@
         <v>17.665175999999999</v>
       </c>
       <c r="D52">
-        <f>(I52-32)*5/9</f>
+        <f>(H52-32)*5/9</f>
         <v>14.419386111111111</v>
       </c>
       <c r="E52">
@@ -4553,7 +4561,7 @@
       <c r="G52">
         <v>2</v>
       </c>
-      <c r="I52">
+      <c r="H52">
         <v>57.954895</v>
       </c>
     </row>
@@ -4568,7 +4576,7 @@
         <v>14.169477000000001</v>
       </c>
       <c r="D53">
-        <f>(I53-32)*5/9</f>
+        <f>(H53-32)*5/9</f>
         <v>21.317265555555554</v>
       </c>
       <c r="E53">
@@ -4580,7 +4588,7 @@
       <c r="G53">
         <v>2</v>
       </c>
-      <c r="I53">
+      <c r="H53">
         <v>70.371077999999997</v>
       </c>
     </row>
@@ -4595,7 +4603,7 @@
         <v>12.555569</v>
       </c>
       <c r="D54">
-        <f>(I54-32)*5/9</f>
+        <f>(H54-32)*5/9</f>
         <v>23.636856111111108</v>
       </c>
       <c r="E54">
@@ -4607,7 +4615,7 @@
       <c r="G54">
         <v>5</v>
       </c>
-      <c r="I54">
+      <c r="H54">
         <v>74.546340999999998</v>
       </c>
     </row>
@@ -4622,7 +4630,7 @@
         <v>11.398597000000001</v>
       </c>
       <c r="D55">
-        <f>(I55-32)*5/9</f>
+        <f>(H55-32)*5/9</f>
         <v>23.006451666666667</v>
       </c>
       <c r="E55">
@@ -4634,7 +4642,7 @@
       <c r="G55">
         <v>4</v>
       </c>
-      <c r="I55">
+      <c r="H55">
         <v>73.411613000000003</v>
       </c>
     </row>
@@ -4649,7 +4657,7 @@
         <v>9.4694090000000006</v>
       </c>
       <c r="D56">
-        <f>(I56-32)*5/9</f>
+        <f>(H56-32)*5/9</f>
         <v>27.10271222222222</v>
       </c>
       <c r="E56">
@@ -4661,7 +4669,7 @@
       <c r="G56">
         <v>6</v>
       </c>
-      <c r="I56">
+      <c r="H56">
         <v>80.784881999999996</v>
       </c>
     </row>
@@ -4676,7 +4684,7 @@
         <v>7.7573340000000002</v>
       </c>
       <c r="D57">
-        <f>(I57-32)*5/9</f>
+        <f>(H57-32)*5/9</f>
         <v>19.610154999999995</v>
       </c>
       <c r="E57">
@@ -4688,7 +4696,7 @@
       <c r="G57">
         <v>5</v>
       </c>
-      <c r="I57">
+      <c r="H57">
         <v>67.298278999999994</v>
       </c>
     </row>
@@ -4703,7 +4711,7 @@
         <v>2.7063190000000001</v>
       </c>
       <c r="D58">
-        <f>(I58-32)*5/9</f>
+        <f>(H58-32)*5/9</f>
         <v>22.764159444444445</v>
       </c>
       <c r="E58">
@@ -4715,7 +4723,7 @@
       <c r="G58">
         <v>4</v>
       </c>
-      <c r="I58">
+      <c r="H58">
         <v>72.975487000000001</v>
       </c>
     </row>
@@ -4730,7 +4738,7 @@
         <v>5.686604</v>
       </c>
       <c r="D59">
-        <f>(I59-32)*5/9</f>
+        <f>(H59-32)*5/9</f>
         <v>7.7248722222222215</v>
       </c>
       <c r="E59">
@@ -4742,7 +4750,7 @@
       <c r="G59">
         <v>6</v>
       </c>
-      <c r="I59">
+      <c r="H59">
         <v>45.904769999999999</v>
       </c>
     </row>
@@ -4757,7 +4765,7 @@
         <v>7.4496349999999998</v>
       </c>
       <c r="D60">
-        <f>(I60-32)*5/9</f>
+        <f>(H60-32)*5/9</f>
         <v>2.1895005555555573</v>
       </c>
       <c r="E60">
@@ -4769,7 +4777,7 @@
       <c r="G60">
         <v>5</v>
       </c>
-      <c r="I60">
+      <c r="H60">
         <v>35.941101000000003</v>
       </c>
     </row>
@@ -4784,7 +4792,7 @@
         <v>7.0996129999999997</v>
       </c>
       <c r="D61">
-        <f>(I61-32)*5/9</f>
+        <f>(H61-32)*5/9</f>
         <v>1.2716249999999993</v>
       </c>
       <c r="E61">
@@ -4796,7 +4804,7 @@
       <c r="G61">
         <v>4</v>
       </c>
-      <c r="I61">
+      <c r="H61">
         <v>34.288924999999999</v>
       </c>
     </row>
@@ -4811,7 +4819,7 @@
         <v>12.831696000000001</v>
       </c>
       <c r="D62">
-        <f>(I62-32)*5/9</f>
+        <f>(H62-32)*5/9</f>
         <v>9.4122316666666652</v>
       </c>
       <c r="E62">
@@ -4823,7 +4831,7 @@
       <c r="G62">
         <v>3</v>
       </c>
-      <c r="I62">
+      <c r="H62">
         <v>48.942017</v>
       </c>
     </row>
@@ -4838,7 +4846,7 @@
         <v>14.560359999999999</v>
       </c>
       <c r="D63">
-        <f>(I63-32)*5/9</f>
+        <f>(H63-32)*5/9</f>
         <v>8.2819811111111132</v>
       </c>
       <c r="E63">
@@ -4850,7 +4858,7 @@
       <c r="G63">
         <v>2</v>
       </c>
-      <c r="I63">
+      <c r="H63">
         <v>46.907566000000003</v>
       </c>
     </row>
@@ -4865,7 +4873,7 @@
         <v>14.194115999999999</v>
       </c>
       <c r="D64">
-        <f>(I64-32)*5/9</f>
+        <f>(H64-32)*5/9</f>
         <v>14.761871666666666</v>
       </c>
       <c r="E64">
@@ -4877,7 +4885,7 @@
       <c r="G64">
         <v>1</v>
       </c>
-      <c r="I64">
+      <c r="H64">
         <v>58.571368999999997</v>
       </c>
     </row>
@@ -4892,7 +4900,7 @@
         <v>15.012734999999999</v>
       </c>
       <c r="D65">
-        <f>(I65-32)*5/9</f>
+        <f>(H65-32)*5/9</f>
         <v>21.290143333333337</v>
       </c>
       <c r="E65">
@@ -4904,7 +4912,7 @@
       <c r="G65">
         <v>0</v>
       </c>
-      <c r="I65">
+      <c r="H65">
         <v>70.322258000000005</v>
       </c>
     </row>
@@ -4919,7 +4927,7 @@
         <v>15.753095999999999</v>
       </c>
       <c r="D66">
-        <f>(I66-32)*5/9</f>
+        <f>(H66-32)*5/9</f>
         <v>24.267531666666667</v>
       </c>
       <c r="E66">
@@ -4931,7 +4939,7 @@
       <c r="G66">
         <v>0</v>
       </c>
-      <c r="I66">
+      <c r="H66">
         <v>75.681556999999998</v>
       </c>
     </row>
@@ -4946,7 +4954,7 @@
         <v>9.6945979999999992</v>
       </c>
       <c r="D67">
-        <f>(I67-32)*5/9</f>
+        <f>(H67-32)*5/9</f>
         <v>27.720396111111114</v>
       </c>
       <c r="E67">
@@ -4958,7 +4966,7 @@
       <c r="G67">
         <v>1</v>
       </c>
-      <c r="I67">
+      <c r="H67">
         <v>81.896713000000005</v>
       </c>
     </row>
@@ -4973,7 +4981,7 @@
         <v>10.148592000000001</v>
       </c>
       <c r="D68">
-        <f>(I68-32)*5/9</f>
+        <f>(H68-32)*5/9</f>
         <v>29.990713333333336</v>
       </c>
       <c r="E68">
@@ -4985,7 +4993,7 @@
       <c r="G68">
         <v>1</v>
       </c>
-      <c r="I68">
+      <c r="H68">
         <v>85.983283999999998</v>
       </c>
     </row>
@@ -5000,7 +5008,7 @@
         <v>7.6750959999999999</v>
       </c>
       <c r="D69">
-        <f>(I69-32)*5/9</f>
+        <f>(H69-32)*5/9</f>
         <v>27.090492222222217</v>
       </c>
       <c r="E69">
@@ -5012,7 +5020,7 @@
       <c r="G69">
         <v>2</v>
       </c>
-      <c r="I69">
+      <c r="H69">
         <v>80.762885999999995</v>
       </c>
     </row>
@@ -5027,7 +5035,7 @@
         <v>6.1388280000000002</v>
       </c>
       <c r="D70">
-        <f>(I70-32)*5/9</f>
+        <f>(H70-32)*5/9</f>
         <v>22.913165555555551</v>
       </c>
       <c r="E70">
@@ -5039,7 +5047,7 @@
       <c r="G70">
         <v>2</v>
       </c>
-      <c r="I70">
+      <c r="H70">
         <v>73.243697999999995</v>
       </c>
     </row>
@@ -5054,7 +5062,7 @@
         <v>2.8603170000000002</v>
       </c>
       <c r="D71">
-        <f>(I71-32)*5/9</f>
+        <f>(H71-32)*5/9</f>
         <v>12.649328333333333</v>
       </c>
       <c r="E71">
@@ -5066,7 +5074,7 @@
       <c r="G71">
         <v>2</v>
       </c>
-      <c r="I71">
+      <c r="H71">
         <v>54.768791</v>
       </c>
     </row>
@@ -5081,7 +5089,7 @@
         <v>4.0653370000000004</v>
       </c>
       <c r="D72">
-        <f>(I72-32)*5/9</f>
+        <f>(H72-32)*5/9</f>
         <v>12.020467222222221</v>
       </c>
       <c r="E72">
@@ -5093,7 +5101,7 @@
       <c r="G72">
         <v>2</v>
       </c>
-      <c r="I72">
+      <c r="H72">
         <v>53.636840999999997</v>
       </c>
     </row>
@@ -5108,7 +5116,7 @@
         <v>8.9650060000000007</v>
       </c>
       <c r="D73">
-        <f>(I73-32)*5/9</f>
+        <f>(H73-32)*5/9</f>
         <v>2.0235361111111101</v>
       </c>
       <c r="E73">
@@ -5120,7 +5128,7 @@
       <c r="G73">
         <v>1</v>
       </c>
-      <c r="I73">
+      <c r="H73">
         <v>35.642364999999998</v>
       </c>
     </row>
@@ -5135,7 +5143,7 @@
         <v>10.820383</v>
       </c>
       <c r="D74">
-        <f>(I74-32)*5/9</f>
+        <f>(H74-32)*5/9</f>
         <v>7.0521566666666677</v>
       </c>
       <c r="E74">
@@ -5147,7 +5155,7 @@
       <c r="G74">
         <v>0</v>
       </c>
-      <c r="I74">
+      <c r="H74">
         <v>44.693882000000002</v>
       </c>
     </row>
@@ -5162,7 +5170,7 @@
         <v>12.539285</v>
       </c>
       <c r="D75">
-        <f>(I75-32)*5/9</f>
+        <f>(H75-32)*5/9</f>
         <v>4.714679444444446</v>
       </c>
       <c r="E75">
@@ -5174,7 +5182,7 @@
       <c r="G75">
         <v>1</v>
       </c>
-      <c r="I75">
+      <c r="H75">
         <v>40.486423000000002</v>
       </c>
     </row>
@@ -5189,7 +5197,7 @@
         <v>16.400084</v>
       </c>
       <c r="D76">
-        <f>(I76-32)*5/9</f>
+        <f>(H76-32)*5/9</f>
         <v>9.6093049999999991</v>
       </c>
       <c r="E76">
@@ -5201,7 +5209,7 @@
       <c r="G76">
         <v>1</v>
       </c>
-      <c r="I76">
+      <c r="H76">
         <v>49.296748999999998</v>
       </c>
     </row>
@@ -5216,7 +5224,7 @@
         <v>14.915723</v>
       </c>
       <c r="D77">
-        <f>(I77-32)*5/9</f>
+        <f>(H77-32)*5/9</f>
         <v>23.669832222222226</v>
       </c>
       <c r="E77">
@@ -5228,7 +5236,7 @@
       <c r="G77">
         <v>2</v>
       </c>
-      <c r="I77">
+      <c r="H77">
         <v>74.605698000000004</v>
       </c>
     </row>
@@ -5243,7 +5251,7 @@
         <v>12.695762999999999</v>
       </c>
       <c r="D78">
-        <f>(I78-32)*5/9</f>
+        <f>(H78-32)*5/9</f>
         <v>25.848613333333329</v>
       </c>
       <c r="E78">
@@ -5255,7 +5263,7 @@
       <c r="G78">
         <v>2</v>
       </c>
-      <c r="I78">
+      <c r="H78">
         <v>78.527503999999993</v>
       </c>
     </row>
@@ -5270,7 +5278,7 @@
         <v>13.330187</v>
       </c>
       <c r="D79">
-        <f>(I79-32)*5/9</f>
+        <f>(H79-32)*5/9</f>
         <v>27.316284444444445</v>
       </c>
       <c r="E79">
@@ -5282,7 +5290,7 @@
       <c r="G79">
         <v>2</v>
       </c>
-      <c r="I79">
+      <c r="H79">
         <v>81.169312000000005</v>
       </c>
     </row>
@@ -5297,7 +5305,7 @@
         <v>9.8378230000000002</v>
       </c>
       <c r="D80">
-        <f>(I80-32)*5/9</f>
+        <f>(H80-32)*5/9</f>
         <v>24.469739999999994</v>
       </c>
       <c r="E80">
@@ -5309,7 +5317,7 @@
       <c r="G80">
         <v>2</v>
       </c>
-      <c r="I80">
+      <c r="H80">
         <v>76.045531999999994</v>
       </c>
     </row>
@@ -5324,7 +5332,7 @@
         <v>5.1371310000000001</v>
       </c>
       <c r="D81">
-        <f>(I81-32)*5/9</f>
+        <f>(H81-32)*5/9</f>
         <v>17.892646666666671</v>
       </c>
       <c r="E81">
@@ -5336,7 +5344,7 @@
       <c r="G81">
         <v>1</v>
       </c>
-      <c r="I81">
+      <c r="H81">
         <v>64.206764000000007</v>
       </c>
     </row>
@@ -5351,7 +5359,7 @@
         <v>3.140012</v>
       </c>
       <c r="D82">
-        <f>(I82-32)*5/9</f>
+        <f>(H82-32)*5/9</f>
         <v>22.134022222222221</v>
       </c>
       <c r="E82">
@@ -5363,7 +5371,7 @@
       <c r="G82">
         <v>0</v>
       </c>
-      <c r="I82">
+      <c r="H82">
         <v>71.841239999999999</v>
       </c>
     </row>
@@ -5378,7 +5386,7 @@
         <v>4.1321880000000002</v>
       </c>
       <c r="D83">
-        <f>(I83-32)*5/9</f>
+        <f>(H83-32)*5/9</f>
         <v>12.490346666666667</v>
       </c>
       <c r="E83">
@@ -5390,7 +5398,7 @@
       <c r="G83">
         <v>0</v>
       </c>
-      <c r="I83">
+      <c r="H83">
         <v>54.482624000000001</v>
       </c>
     </row>
@@ -5405,7 +5413,7 @@
         <v>4.4875819999999997</v>
       </c>
       <c r="D84">
-        <f>(I84-32)*5/9</f>
+        <f>(H84-32)*5/9</f>
         <v>10.055340555555555</v>
       </c>
       <c r="E84">
@@ -5417,7 +5425,7 @@
       <c r="G84">
         <v>0</v>
       </c>
-      <c r="I84">
+      <c r="H84">
         <v>50.099612999999998</v>
       </c>
     </row>
@@ -5432,7 +5440,7 @@
         <v>8.1030230000000003</v>
       </c>
       <c r="D85">
-        <f>(I85-32)*5/9</f>
+        <f>(H85-32)*5/9</f>
         <v>-0.27846222222222317</v>
       </c>
       <c r="E85">
@@ -5444,7 +5452,7 @@
       <c r="G85">
         <v>0</v>
       </c>
-      <c r="I85">
+      <c r="H85">
         <v>31.498767999999998</v>
       </c>
     </row>
@@ -5459,7 +5467,7 @@
         <v>12.103476000000001</v>
       </c>
       <c r="D86">
-        <f>(I86-32)*5/9</f>
+        <f>(H86-32)*5/9</f>
         <v>6.7556738888888885</v>
       </c>
       <c r="E86">
@@ -5471,7 +5479,7 @@
       <c r="G86">
         <v>1</v>
       </c>
-      <c r="I86">
+      <c r="H86">
         <v>44.160212999999999</v>
       </c>
     </row>
@@ -5486,7 +5494,7 @@
         <v>14.679064</v>
       </c>
       <c r="D87">
-        <f>(I87-32)*5/9</f>
+        <f>(H87-32)*5/9</f>
         <v>4.1946200000000013</v>
       </c>
       <c r="E87">
@@ -5498,7 +5506,7 @@
       <c r="G87">
         <v>1</v>
       </c>
-      <c r="I87">
+      <c r="H87">
         <v>39.550316000000002</v>
       </c>
     </row>
@@ -5513,7 +5521,7 @@
         <v>15.109052999999999</v>
       </c>
       <c r="D88">
-        <f>(I88-32)*5/9</f>
+        <f>(H88-32)*5/9</f>
         <v>15.24344777777778</v>
       </c>
       <c r="E88">
@@ -5525,7 +5533,7 @@
       <c r="G88">
         <v>2</v>
       </c>
-      <c r="I88">
+      <c r="H88">
         <v>59.438206000000001</v>
       </c>
     </row>
@@ -5540,7 +5548,7 @@
         <v>17.479212</v>
       </c>
       <c r="D89">
-        <f>(I89-32)*5/9</f>
+        <f>(H89-32)*5/9</f>
         <v>15.122576666666667</v>
       </c>
       <c r="E89">
@@ -5552,7 +5560,7 @@
       <c r="G89">
         <v>2</v>
       </c>
-      <c r="I89">
+      <c r="H89">
         <v>59.220638000000001</v>
       </c>
     </row>
@@ -5567,7 +5575,7 @@
         <v>13.271703</v>
       </c>
       <c r="D90">
-        <f>(I90-32)*5/9</f>
+        <f>(H90-32)*5/9</f>
         <v>25.113745555555553</v>
       </c>
       <c r="E90">
@@ -5579,7 +5587,7 @@
       <c r="G90">
         <v>2</v>
       </c>
-      <c r="I90">
+      <c r="H90">
         <v>77.204741999999996</v>
       </c>
     </row>
@@ -5594,7 +5602,7 @@
         <v>10.594901999999999</v>
       </c>
       <c r="D91">
-        <f>(I91-32)*5/9</f>
+        <f>(H91-32)*5/9</f>
         <v>21.706322777777778</v>
       </c>
       <c r="E91">
@@ -5606,7 +5614,7 @@
       <c r="G91">
         <v>1</v>
       </c>
-      <c r="I91">
+      <c r="H91">
         <v>71.071381000000002</v>
       </c>
     </row>
@@ -5621,7 +5629,7 @@
         <v>6.8220460000000003</v>
       </c>
       <c r="D92">
-        <f>(I92-32)*5/9</f>
+        <f>(H92-32)*5/9</f>
         <v>28.356115555555558</v>
       </c>
       <c r="E92">
@@ -5633,7 +5641,7 @@
       <c r="G92">
         <v>0</v>
       </c>
-      <c r="I92">
+      <c r="H92">
         <v>83.041008000000005</v>
       </c>
     </row>
@@ -5648,7 +5656,7 @@
         <v>6.0641210000000001</v>
       </c>
       <c r="D93">
-        <f>(I93-32)*5/9</f>
+        <f>(H93-32)*5/9</f>
         <v>21.874529444444448</v>
       </c>
       <c r="E93">
@@ -5660,7 +5668,7 @@
       <c r="G93">
         <v>0</v>
       </c>
-      <c r="I93">
+      <c r="H93">
         <v>71.374153000000007</v>
       </c>
     </row>
@@ -5675,7 +5683,7 @@
         <v>3.359556</v>
       </c>
       <c r="D94">
-        <f>(I94-32)*5/9</f>
+        <f>(H94-32)*5/9</f>
         <v>20.281948333333336</v>
       </c>
       <c r="E94">
@@ -5687,7 +5695,7 @@
       <c r="G94">
         <v>0</v>
       </c>
-      <c r="I94">
+      <c r="H94">
         <v>68.507507000000004</v>
       </c>
     </row>
@@ -5702,7 +5710,7 @@
         <v>3.5230130000000002</v>
       </c>
       <c r="D95">
-        <f>(I95-32)*5/9</f>
+        <f>(H95-32)*5/9</f>
         <v>10.328449444444443</v>
       </c>
       <c r="E95">
@@ -5714,7 +5722,7 @@
       <c r="G95">
         <v>0</v>
       </c>
-      <c r="I95">
+      <c r="H95">
         <v>50.591208999999999</v>
       </c>
     </row>
@@ -5729,7 +5737,7 @@
         <v>3.7716729999999998</v>
       </c>
       <c r="D96">
-        <f>(I96-32)*5/9</f>
+        <f>(H96-32)*5/9</f>
         <v>13.080628888888889</v>
       </c>
       <c r="E96">
@@ -5741,7 +5749,7 @@
       <c r="G96">
         <v>0</v>
       </c>
-      <c r="I96">
+      <c r="H96">
         <v>55.545132000000002</v>
       </c>
     </row>
@@ -5756,7 +5764,7 @@
         <v>7.1998920000000002</v>
       </c>
       <c r="D97">
-        <f>(I97-32)*5/9</f>
+        <f>(H97-32)*5/9</f>
         <v>2.95059</v>
       </c>
       <c r="E97">
@@ -5768,7 +5776,7 @@
       <c r="G97">
         <v>0</v>
       </c>
-      <c r="I97">
+      <c r="H97">
         <v>37.311062</v>
       </c>
     </row>

--- a/project2/Project2.xlsx
+++ b/project2/Project2.xlsx
@@ -24,13 +24,13 @@
     <t xml:space="preserve"> Month</t>
   </si>
   <si>
-    <t xml:space="preserve"> Precipitation</t>
+    <t xml:space="preserve"> Precipitation (inch)</t>
   </si>
   <si>
-    <t xml:space="preserve">Temp C</t>
+    <t xml:space="preserve">Temp (C)</t>
   </si>
   <si>
-    <t xml:space="preserve"> Grain Height</t>
+    <t xml:space="preserve"> Grain Height (inch)</t>
   </si>
   <si>
     <t xml:space="preserve"> Num Deer</t>
@@ -114,17 +114,7 @@
           <a:bodyPr/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" spc="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
               <a:rPr/>
@@ -187,7 +177,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v xml:space="preserve"> Precipitation</c:v>
+                  <c:v xml:space="preserve"> Precipitation (inch)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -517,7 +507,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Temp C</c:v>
+                  <c:v>Temp (C)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -847,7 +837,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v xml:space="preserve"> Grain Height</c:v>
+                  <c:v xml:space="preserve"> Grain Height (inch)</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1828,14 +1818,6 @@
           </c:val>
           <c:smooth val="0"/>
         </c:ser>
-        <c:dLbls>
-          <c:showBubbleSize val="0"/>
-          <c:showCatName val="0"/>
-          <c:showLegendKey val="0"/>
-          <c:showPercent val="0"/>
-          <c:showSerName val="0"/>
-          <c:showVal val="0"/>
-        </c:dLbls>
         <c:marker val="0"/>
         <c:smooth val="0"/>
         <c:axId val="2140841519"/>
@@ -1848,6 +1830,63 @@
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr/>
+                  <a:t>Months</a:t>
+                </a:r>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="out"/>
@@ -1878,9 +1917,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr/>
@@ -1891,12 +1930,15 @@
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
         <c:lblOffset val="100"/>
+        <c:tickLblSkip val="2"/>
+        <c:tickMarkSkip val="2"/>
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
         <c:axId val="2140841520"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:min val="0.000000"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -1917,6 +1959,63 @@
             </a:ln>
           </c:spPr>
         </c:majorGridlines>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1000">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="65000"/>
+                        <a:lumOff val="35000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:r>
+                  <a:rPr/>
+                  <a:t>Units</a:t>
+                </a:r>
+                <a:endParaRPr/>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+          <c:overlay val="0"/>
+          <c:spPr bwMode="auto">
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:txPr>
+            <a:bodyPr/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="1000">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="65000"/>
+                      <a:lumOff val="35000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:latin typeface="+mn-lt"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="+mn-cs"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr/>
+            </a:p>
+          </c:txPr>
+        </c:title>
         <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
@@ -1941,9 +2040,9 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="Calibri"/>
-                <a:ea typeface="Arial"/>
-                <a:cs typeface="Arial"/>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr/>
@@ -2004,8 +2103,8 @@
   </c:chart>
   <c:spPr bwMode="auto">
     <a:xfrm rot="0" flipH="0" flipV="0">
-      <a:off x="6568438" y="723898"/>
-      <a:ext cx="8493011" cy="5084444"/>
+      <a:off x="6278879" y="723897"/>
+      <a:ext cx="13481684" cy="5684521"/>
     </a:xfrm>
     <a:prstGeom prst="rect">
       <a:avLst/>
@@ -2640,15 +2739,15 @@
   <xdr:twoCellAnchor editAs="twoCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>899158</xdr:colOff>
+      <xdr:colOff>609599</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>175258</xdr:rowOff>
+      <xdr:rowOff>175257</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>552969</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>139062</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>70484</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>7619</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
       <xdr:nvGraphicFramePr>
@@ -2658,8 +2757,8 @@
         </xdr:cNvGraphicFramePr>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm rot="0" flipH="0" flipV="0">
-        <a:off x="6568438" y="723898"/>
-        <a:ext cx="8493011" cy="5084444"/>
+        <a:off x="6278879" y="723897"/>
+        <a:ext cx="13481684" cy="5684521"/>
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
@@ -3199,7 +3298,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <f>(H2-32)*5/9</f>
+        <f t="shared" ref="D2:D9" si="0">(H2-32)*5/9</f>
         <v>-17.777777777777779</v>
       </c>
       <c r="E2">
@@ -3226,7 +3325,7 @@
         <v>15.375037000000001</v>
       </c>
       <c r="D3">
-        <f>(H3-32)*5/9</f>
+        <f t="shared" si="0"/>
         <v>6.5252900000000009</v>
       </c>
       <c r="E3">
@@ -3253,7 +3352,7 @@
         <v>14.585760000000001</v>
       </c>
       <c r="D4">
-        <f>(H4-32)*5/9</f>
+        <f t="shared" si="0"/>
         <v>17.25364888888889</v>
       </c>
       <c r="E4">
@@ -3280,7 +3379,7 @@
         <v>14.906654</v>
       </c>
       <c r="D5">
-        <f>(H5-32)*5/9</f>
+        <f t="shared" si="0"/>
         <v>21.411653888888889</v>
       </c>
       <c r="E5">
@@ -3307,7 +3406,7 @@
         <v>14.758124</v>
       </c>
       <c r="D6">
-        <f>(H6-32)*5/9</f>
+        <f t="shared" si="0"/>
         <v>23.161154999999997</v>
       </c>
       <c r="E6">
@@ -3334,7 +3433,7 @@
         <v>13.361834</v>
       </c>
       <c r="D7">
-        <f>(H7-32)*5/9</f>
+        <f t="shared" si="0"/>
         <v>26.436962777777779</v>
       </c>
       <c r="E7">
@@ -3361,7 +3460,7 @@
         <v>9.3162730000000007</v>
       </c>
       <c r="D8">
-        <f>(H8-32)*5/9</f>
+        <f t="shared" si="0"/>
         <v>27.795969444444449</v>
       </c>
       <c r="E8">
@@ -3388,7 +3487,7 @@
         <v>3.822562</v>
       </c>
       <c r="D9">
-        <f>(H9-32)*5/9</f>
+        <f t="shared" si="0"/>
         <v>24.600838333333332</v>
       </c>
       <c r="E9">
@@ -3415,7 +3514,7 @@
         <v>5.4211520000000002</v>
       </c>
       <c r="D10">
-        <f>(H10-32)*5/9</f>
+        <f t="shared" ref="D10:D73" si="1">(H10-32)*5/9</f>
         <v>14.400560555555554</v>
       </c>
       <c r="E10">
@@ -3442,7 +3541,7 @@
         <v>2.7236069999999999</v>
       </c>
       <c r="D11">
-        <f>(H11-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>11.57917</v>
       </c>
       <c r="E11">
@@ -3469,7 +3568,7 @@
         <v>4.6303859999999997</v>
       </c>
       <c r="D12">
-        <f>(H12-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>13.242420555555555</v>
       </c>
       <c r="E12">
@@ -3496,7 +3595,7 @@
         <v>8.8976469999999992</v>
       </c>
       <c r="D13">
-        <f>(H13-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>8.5909566666666635</v>
       </c>
       <c r="E13">
@@ -3523,7 +3622,7 @@
         <v>11.650064</v>
       </c>
       <c r="D14">
-        <f>(H14-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>6.3514050000000015</v>
       </c>
       <c r="E14">
@@ -3550,7 +3649,7 @@
         <v>13.412706999999999</v>
       </c>
       <c r="D15">
-        <f>(H15-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>12.951870000000001</v>
       </c>
       <c r="E15">
@@ -3577,7 +3676,7 @@
         <v>16.875209999999999</v>
       </c>
       <c r="D16">
-        <f>(H16-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>12.976956111111113</v>
       </c>
       <c r="E16">
@@ -3604,7 +3703,7 @@
         <v>14.928813999999999</v>
       </c>
       <c r="D17">
-        <f>(H17-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>22.781651666666669</v>
       </c>
       <c r="E17">
@@ -3631,7 +3730,7 @@
         <v>15.918747</v>
       </c>
       <c r="D18">
-        <f>(H18-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>26.831461666666669</v>
       </c>
       <c r="E18">
@@ -3658,7 +3757,7 @@
         <v>11.656897000000001</v>
       </c>
       <c r="D19">
-        <f>(H19-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>31.280585555555554</v>
       </c>
       <c r="E19">
@@ -3685,7 +3784,7 @@
         <v>9.0999929999999996</v>
       </c>
       <c r="D20">
-        <f>(H20-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>22.868215555555558</v>
       </c>
       <c r="E20">
@@ -3712,7 +3811,7 @@
         <v>4.0140450000000003</v>
       </c>
       <c r="D21">
-        <f>(H21-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>21.733330555555558</v>
       </c>
       <c r="E21">
@@ -3739,7 +3838,7 @@
         <v>2.4568279999999998</v>
       </c>
       <c r="D22">
-        <f>(H22-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>17.961341111111114</v>
       </c>
       <c r="E22">
@@ -3766,7 +3865,7 @@
         <v>5.8132770000000002</v>
       </c>
       <c r="D23">
-        <f>(H23-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>17.909054444444447</v>
       </c>
       <c r="E23">
@@ -3793,7 +3892,7 @@
         <v>5.9164000000000003</v>
       </c>
       <c r="D24">
-        <f>(H24-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>5.1062138888888873</v>
       </c>
       <c r="E24">
@@ -3820,7 +3919,7 @@
         <v>8.4972290000000008</v>
       </c>
       <c r="D25">
-        <f>(H25-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>7.7146977777777801</v>
       </c>
       <c r="E25">
@@ -3847,7 +3946,7 @@
         <v>9.7100360000000006</v>
       </c>
       <c r="D26">
-        <f>(H26-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>5.1742300000000006</v>
       </c>
       <c r="E26">
@@ -3874,7 +3973,7 @@
         <v>15.965878999999999</v>
       </c>
       <c r="D27">
-        <f>(H27-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>12.496982222222222</v>
       </c>
       <c r="E27">
@@ -3901,7 +4000,7 @@
         <v>16.749693000000001</v>
       </c>
       <c r="D28">
-        <f>(H28-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>10.283048333333333</v>
       </c>
       <c r="E28">
@@ -3928,7 +4027,7 @@
         <v>16.547001000000002</v>
       </c>
       <c r="D29">
-        <f>(H29-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>16.809643888888889</v>
       </c>
       <c r="E29">
@@ -3955,7 +4054,7 @@
         <v>15.762941</v>
       </c>
       <c r="D30">
-        <f>(H30-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>22.746793888888892</v>
       </c>
       <c r="E30">
@@ -3982,7 +4081,7 @@
         <v>10.468787000000001</v>
       </c>
       <c r="D31">
-        <f>(H31-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>24.402919444444446</v>
       </c>
       <c r="E31">
@@ -4009,7 +4108,7 @@
         <v>9.1937650000000009</v>
       </c>
       <c r="D32">
-        <f>(H32-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>24.625396666666671</v>
       </c>
       <c r="E32">
@@ -4036,7 +4135,7 @@
         <v>6.3865759999999998</v>
       </c>
       <c r="D33">
-        <f>(H33-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>24.397188888888891</v>
       </c>
       <c r="E33">
@@ -4063,7 +4162,7 @@
         <v>5.9003240000000003</v>
       </c>
       <c r="D34">
-        <f>(H34-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>17.759763888888887</v>
       </c>
       <c r="E34">
@@ -4090,7 +4189,7 @@
         <v>4.941319</v>
       </c>
       <c r="D35">
-        <f>(H35-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>16.177198888888888</v>
       </c>
       <c r="E35">
@@ -4117,7 +4216,7 @@
         <v>4.6206579999999997</v>
       </c>
       <c r="D36">
-        <f>(H36-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>7.5042683333333331</v>
       </c>
       <c r="E36">
@@ -4144,7 +4243,7 @@
         <v>7.0377270000000003</v>
       </c>
       <c r="D37">
-        <f>(H37-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>9.4911361111111123</v>
       </c>
       <c r="E37">
@@ -4171,7 +4270,7 @@
         <v>11.280728</v>
       </c>
       <c r="D38">
-        <f>(H38-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>6.3906100000000006</v>
       </c>
       <c r="E38">
@@ -4198,7 +4297,7 @@
         <v>15.386649</v>
       </c>
       <c r="D39">
-        <f>(H39-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>5.2661405555555554</v>
       </c>
       <c r="E39">
@@ -4225,7 +4324,7 @@
         <v>14.699982</v>
       </c>
       <c r="D40">
-        <f>(H40-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>12.091272222222223</v>
       </c>
       <c r="E40">
@@ -4252,7 +4351,7 @@
         <v>16.021329999999999</v>
       </c>
       <c r="D41">
-        <f>(H41-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>15.945042777777777</v>
       </c>
       <c r="E41">
@@ -4279,7 +4378,7 @@
         <v>15.869856</v>
       </c>
       <c r="D42">
-        <f>(H42-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>19.741266111111109</v>
       </c>
       <c r="E42">
@@ -4306,7 +4405,7 @@
         <v>11.534691</v>
       </c>
       <c r="D43">
-        <f>(H43-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>22.133343888888888</v>
       </c>
       <c r="E43">
@@ -4333,7 +4432,7 @@
         <v>10.187101</v>
       </c>
       <c r="D44">
-        <f>(H44-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>31.674190000000003</v>
       </c>
       <c r="E44">
@@ -4360,7 +4459,7 @@
         <v>6.756443</v>
       </c>
       <c r="D45">
-        <f>(H45-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>22.114389444444448</v>
       </c>
       <c r="E45">
@@ -4387,7 +4486,7 @@
         <v>3.1334909999999998</v>
       </c>
       <c r="D46">
-        <f>(H46-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>16.144214444444444</v>
       </c>
       <c r="E46">
@@ -4414,7 +4513,7 @@
         <v>2.8140040000000002</v>
       </c>
       <c r="D47">
-        <f>(H47-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>9.8399311111111079</v>
       </c>
       <c r="E47">
@@ -4441,7 +4540,7 @@
         <v>6.9312399999999998</v>
       </c>
       <c r="D48">
-        <f>(H48-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>3.5374261111111118</v>
       </c>
       <c r="E48">
@@ -4468,7 +4567,7 @@
         <v>6.7452059999999996</v>
       </c>
       <c r="D49">
-        <f>(H49-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>7.546060555555556</v>
       </c>
       <c r="E49">
@@ -4495,7 +4594,7 @@
         <v>11.639168</v>
       </c>
       <c r="D50">
-        <f>(H50-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>-0.14885055555555601</v>
       </c>
       <c r="E50">
@@ -4522,7 +4621,7 @@
         <v>15.433832000000001</v>
       </c>
       <c r="D51">
-        <f>(H51-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>4.8106172222222234</v>
       </c>
       <c r="E51">
@@ -4549,7 +4648,7 @@
         <v>17.665175999999999</v>
       </c>
       <c r="D52">
-        <f>(H52-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>14.419386111111111</v>
       </c>
       <c r="E52">
@@ -4576,7 +4675,7 @@
         <v>14.169477000000001</v>
       </c>
       <c r="D53">
-        <f>(H53-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>21.317265555555554</v>
       </c>
       <c r="E53">
@@ -4603,7 +4702,7 @@
         <v>12.555569</v>
       </c>
       <c r="D54">
-        <f>(H54-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>23.636856111111108</v>
       </c>
       <c r="E54">
@@ -4630,7 +4729,7 @@
         <v>11.398597000000001</v>
       </c>
       <c r="D55">
-        <f>(H55-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>23.006451666666667</v>
       </c>
       <c r="E55">
@@ -4657,7 +4756,7 @@
         <v>9.4694090000000006</v>
       </c>
       <c r="D56">
-        <f>(H56-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>27.10271222222222</v>
       </c>
       <c r="E56">
@@ -4684,7 +4783,7 @@
         <v>7.7573340000000002</v>
       </c>
       <c r="D57">
-        <f>(H57-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>19.610154999999995</v>
       </c>
       <c r="E57">
@@ -4711,7 +4810,7 @@
         <v>2.7063190000000001</v>
       </c>
       <c r="D58">
-        <f>(H58-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>22.764159444444445</v>
       </c>
       <c r="E58">
@@ -4738,7 +4837,7 @@
         <v>5.686604</v>
       </c>
       <c r="D59">
-        <f>(H59-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>7.7248722222222215</v>
       </c>
       <c r="E59">
@@ -4765,7 +4864,7 @@
         <v>7.4496349999999998</v>
       </c>
       <c r="D60">
-        <f>(H60-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>2.1895005555555573</v>
       </c>
       <c r="E60">
@@ -4792,7 +4891,7 @@
         <v>7.0996129999999997</v>
       </c>
       <c r="D61">
-        <f>(H61-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>1.2716249999999993</v>
       </c>
       <c r="E61">
@@ -4819,7 +4918,7 @@
         <v>12.831696000000001</v>
       </c>
       <c r="D62">
-        <f>(H62-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>9.4122316666666652</v>
       </c>
       <c r="E62">
@@ -4846,7 +4945,7 @@
         <v>14.560359999999999</v>
       </c>
       <c r="D63">
-        <f>(H63-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>8.2819811111111132</v>
       </c>
       <c r="E63">
@@ -4873,7 +4972,7 @@
         <v>14.194115999999999</v>
       </c>
       <c r="D64">
-        <f>(H64-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>14.761871666666666</v>
       </c>
       <c r="E64">
@@ -4900,7 +4999,7 @@
         <v>15.012734999999999</v>
       </c>
       <c r="D65">
-        <f>(H65-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>21.290143333333337</v>
       </c>
       <c r="E65">
@@ -4927,7 +5026,7 @@
         <v>15.753095999999999</v>
       </c>
       <c r="D66">
-        <f>(H66-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>24.267531666666667</v>
       </c>
       <c r="E66">
@@ -4954,7 +5053,7 @@
         <v>9.6945979999999992</v>
       </c>
       <c r="D67">
-        <f>(H67-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>27.720396111111114</v>
       </c>
       <c r="E67">
@@ -4981,7 +5080,7 @@
         <v>10.148592000000001</v>
       </c>
       <c r="D68">
-        <f>(H68-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>29.990713333333336</v>
       </c>
       <c r="E68">
@@ -5008,7 +5107,7 @@
         <v>7.6750959999999999</v>
       </c>
       <c r="D69">
-        <f>(H69-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>27.090492222222217</v>
       </c>
       <c r="E69">
@@ -5035,7 +5134,7 @@
         <v>6.1388280000000002</v>
       </c>
       <c r="D70">
-        <f>(H70-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>22.913165555555551</v>
       </c>
       <c r="E70">
@@ -5062,7 +5161,7 @@
         <v>2.8603170000000002</v>
       </c>
       <c r="D71">
-        <f>(H71-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>12.649328333333333</v>
       </c>
       <c r="E71">
@@ -5089,7 +5188,7 @@
         <v>4.0653370000000004</v>
       </c>
       <c r="D72">
-        <f>(H72-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>12.020467222222221</v>
       </c>
       <c r="E72">
@@ -5116,7 +5215,7 @@
         <v>8.9650060000000007</v>
       </c>
       <c r="D73">
-        <f>(H73-32)*5/9</f>
+        <f t="shared" si="1"/>
         <v>2.0235361111111101</v>
       </c>
       <c r="E73">
@@ -5143,7 +5242,7 @@
         <v>10.820383</v>
       </c>
       <c r="D74">
-        <f>(H74-32)*5/9</f>
+        <f t="shared" ref="D74:D97" si="2">(H74-32)*5/9</f>
         <v>7.0521566666666677</v>
       </c>
       <c r="E74">
@@ -5170,7 +5269,7 @@
         <v>12.539285</v>
       </c>
       <c r="D75">
-        <f>(H75-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>4.714679444444446</v>
       </c>
       <c r="E75">
@@ -5197,7 +5296,7 @@
         <v>16.400084</v>
       </c>
       <c r="D76">
-        <f>(H76-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>9.6093049999999991</v>
       </c>
       <c r="E76">
@@ -5224,7 +5323,7 @@
         <v>14.915723</v>
       </c>
       <c r="D77">
-        <f>(H77-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>23.669832222222226</v>
       </c>
       <c r="E77">
@@ -5251,7 +5350,7 @@
         <v>12.695762999999999</v>
       </c>
       <c r="D78">
-        <f>(H78-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>25.848613333333329</v>
       </c>
       <c r="E78">
@@ -5278,7 +5377,7 @@
         <v>13.330187</v>
       </c>
       <c r="D79">
-        <f>(H79-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>27.316284444444445</v>
       </c>
       <c r="E79">
@@ -5305,7 +5404,7 @@
         <v>9.8378230000000002</v>
       </c>
       <c r="D80">
-        <f>(H80-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>24.469739999999994</v>
       </c>
       <c r="E80">
@@ -5332,7 +5431,7 @@
         <v>5.1371310000000001</v>
       </c>
       <c r="D81">
-        <f>(H81-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>17.892646666666671</v>
       </c>
       <c r="E81">
@@ -5359,7 +5458,7 @@
         <v>3.140012</v>
       </c>
       <c r="D82">
-        <f>(H82-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>22.134022222222221</v>
       </c>
       <c r="E82">
@@ -5386,7 +5485,7 @@
         <v>4.1321880000000002</v>
       </c>
       <c r="D83">
-        <f>(H83-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>12.490346666666667</v>
       </c>
       <c r="E83">
@@ -5413,7 +5512,7 @@
         <v>4.4875819999999997</v>
       </c>
       <c r="D84">
-        <f>(H84-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>10.055340555555555</v>
       </c>
       <c r="E84">
@@ -5440,7 +5539,7 @@
         <v>8.1030230000000003</v>
       </c>
       <c r="D85">
-        <f>(H85-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>-0.27846222222222317</v>
       </c>
       <c r="E85">
@@ -5467,7 +5566,7 @@
         <v>12.103476000000001</v>
       </c>
       <c r="D86">
-        <f>(H86-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>6.7556738888888885</v>
       </c>
       <c r="E86">
@@ -5494,7 +5593,7 @@
         <v>14.679064</v>
       </c>
       <c r="D87">
-        <f>(H87-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>4.1946200000000013</v>
       </c>
       <c r="E87">
@@ -5521,7 +5620,7 @@
         <v>15.109052999999999</v>
       </c>
       <c r="D88">
-        <f>(H88-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>15.24344777777778</v>
       </c>
       <c r="E88">
@@ -5548,7 +5647,7 @@
         <v>17.479212</v>
       </c>
       <c r="D89">
-        <f>(H89-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>15.122576666666667</v>
       </c>
       <c r="E89">
@@ -5575,7 +5674,7 @@
         <v>13.271703</v>
       </c>
       <c r="D90">
-        <f>(H90-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>25.113745555555553</v>
       </c>
       <c r="E90">
@@ -5602,7 +5701,7 @@
         <v>10.594901999999999</v>
       </c>
       <c r="D91">
-        <f>(H91-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>21.706322777777778</v>
       </c>
       <c r="E91">
@@ -5629,7 +5728,7 @@
         <v>6.8220460000000003</v>
       </c>
       <c r="D92">
-        <f>(H92-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>28.356115555555558</v>
       </c>
       <c r="E92">
@@ -5656,7 +5755,7 @@
         <v>6.0641210000000001</v>
       </c>
       <c r="D93">
-        <f>(H93-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>21.874529444444448</v>
       </c>
       <c r="E93">
@@ -5683,7 +5782,7 @@
         <v>3.359556</v>
       </c>
       <c r="D94">
-        <f>(H94-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>20.281948333333336</v>
       </c>
       <c r="E94">
@@ -5710,7 +5809,7 @@
         <v>3.5230130000000002</v>
       </c>
       <c r="D95">
-        <f>(H95-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>10.328449444444443</v>
       </c>
       <c r="E95">
@@ -5737,7 +5836,7 @@
         <v>3.7716729999999998</v>
       </c>
       <c r="D96">
-        <f>(H96-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>13.080628888888889</v>
       </c>
       <c r="E96">
@@ -5764,7 +5863,7 @@
         <v>7.1998920000000002</v>
       </c>
       <c r="D97">
-        <f>(H97-32)*5/9</f>
+        <f t="shared" si="2"/>
         <v>2.95059</v>
       </c>
       <c r="E97">
